--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_14-05-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_14-05-2025.xlsx
@@ -134,6 +134,101 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Price Tracker</author>
+  </authors>
+  <commentList>
+    <comment ref="K2" authorId="0" shapeId="0">
+      <text>
+        <t>£11.97</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>£13.69</t>
+      </text>
+    </comment>
+    <comment ref="K4" authorId="0" shapeId="0">
+      <text>
+        <t>£16.97</t>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>£18.07</t>
+      </text>
+    </comment>
+    <comment ref="K6" authorId="0" shapeId="0">
+      <text>
+        <t>£22.99</t>
+      </text>
+    </comment>
+    <comment ref="K7" authorId="0" shapeId="0">
+      <text>
+        <t>£24.60</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
+      <text>
+        <t>Error: list index out of range</t>
+      </text>
+    </comment>
+    <comment ref="K8" authorId="0" shapeId="0">
+      <text>
+        <t>£25.14</t>
+      </text>
+    </comment>
+    <comment ref="K9" authorId="0" shapeId="0">
+      <text>
+        <t>£28.88</t>
+      </text>
+    </comment>
+    <comment ref="K10" authorId="0" shapeId="0">
+      <text>
+        <t>£31.02</t>
+      </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>£30.75</t>
+      </text>
+    </comment>
+    <comment ref="K12" authorId="0" shapeId="0">
+      <text>
+        <t>£40.65</t>
+      </text>
+    </comment>
+    <comment ref="J13" authorId="0" shapeId="0">
+      <text>
+        <t>Error: list index out of range</t>
+      </text>
+    </comment>
+    <comment ref="K13" authorId="0" shapeId="0">
+      <text>
+        <t>£37.44</t>
+      </text>
+    </comment>
+    <comment ref="K14" authorId="0" shapeId="0">
+      <text>
+        <t>£45.46</t>
+      </text>
+    </comment>
+    <comment ref="K15" authorId="0" shapeId="0">
+      <text>
+        <t>£45.99</t>
+      </text>
+    </comment>
+    <comment ref="K16" authorId="0" shapeId="0">
+      <text>
+        <t>£48.14</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2855,5 +2950,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>